--- a/볼보_models.xlsx
+++ b/볼보_models.xlsx
@@ -677,7 +677,11 @@
         </is>
       </c>
       <c r="I2" s="11" t="inlineStr"/>
-      <c r="J2" s="11" t="inlineStr"/>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>HU56</t>
+        </is>
+      </c>
       <c r="K2" s="11" t="inlineStr"/>
       <c r="L2" s="11" t="inlineStr"/>
       <c r="M2" s="11" t="inlineStr"/>
@@ -688,7 +692,7 @@
       </c>
       <c r="O2" s="11" t="inlineStr">
         <is>
-          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15)</t>
+          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15), UHS·American Key Supply(S40·V40 1996-2004 HU56 2트랙 트랜스폰더 키 ID44)</t>
         </is>
       </c>
       <c r="P2" s="11" t="inlineStr"/>
@@ -735,7 +739,11 @@
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr"/>
-      <c r="J3" s="11" t="inlineStr"/>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>HU56</t>
+        </is>
+      </c>
       <c r="K3" s="11" t="inlineStr"/>
       <c r="L3" s="11" t="inlineStr"/>
       <c r="M3" s="11" t="inlineStr"/>
@@ -746,7 +754,7 @@
       </c>
       <c r="O3" s="11" t="inlineStr">
         <is>
-          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15)</t>
+          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15), UHS·American Key Supply(S40·V40 1996-2004 HU56 2트랙 트랜스폰더 키 ID44)</t>
         </is>
       </c>
       <c r="P3" s="11" t="inlineStr"/>
@@ -793,7 +801,11 @@
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr"/>
-      <c r="J4" s="11" t="inlineStr"/>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>HU56</t>
+        </is>
+      </c>
       <c r="K4" s="11" t="inlineStr"/>
       <c r="L4" s="11" t="inlineStr"/>
       <c r="M4" s="11" t="inlineStr"/>
@@ -804,7 +816,7 @@
       </c>
       <c r="O4" s="11" t="inlineStr">
         <is>
-          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15)</t>
+          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15), UHS·American Key Supply(S40·V40 1996-2004 HU56 2트랙 트랜스폰더 키 ID44)</t>
         </is>
       </c>
       <c r="P4" s="11" t="inlineStr"/>
@@ -851,7 +863,11 @@
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr"/>
-      <c r="J5" s="11" t="inlineStr"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>HU56</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr"/>
       <c r="L5" s="11" t="inlineStr"/>
       <c r="M5" s="11" t="inlineStr"/>
@@ -862,7 +878,7 @@
       </c>
       <c r="O5" s="11" t="inlineStr">
         <is>
-          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15)</t>
+          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15), UHS·American Key Supply(S40·V40 1996-2004 HU56 2트랙 트랜스폰더 키 ID44)</t>
         </is>
       </c>
       <c r="P5" s="11" t="inlineStr"/>
@@ -909,7 +925,11 @@
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr"/>
-      <c r="J6" s="11" t="inlineStr"/>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>HU56</t>
+        </is>
+      </c>
       <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="11" t="inlineStr"/>
       <c r="M6" s="11" t="inlineStr"/>
@@ -920,7 +940,7 @@
       </c>
       <c r="O6" s="11" t="inlineStr">
         <is>
-          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15)</t>
+          <t>transpondery(S40 1998–2004·V40 1998–2004 Philips Crypto ID44 PCF7935, JMA TP14·Silca T15), UHS·American Key Supply(S40·V40 1996-2004 HU56 2트랙 트랜스폰더 키 ID44)</t>
         </is>
       </c>
       <c r="P6" s="11" t="inlineStr"/>
@@ -7976,7 +7996,11 @@
       </c>
       <c r="I111" s="11" t="inlineStr"/>
       <c r="J111" s="11" t="inlineStr"/>
-      <c r="K111" s="11" t="inlineStr"/>
+      <c r="K111" s="11" t="inlineStr">
+        <is>
+          <t>80001529[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="L111" s="11" t="inlineStr"/>
       <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="7" t="inlineStr">
@@ -7986,7 +8010,7 @@
       </c>
       <c r="O111" s="11" t="inlineStr">
         <is>
-          <t>오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
+          <t>볼보 부품 카탈로그(EX30 Key Card 80001529, CH-624564), 오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
         </is>
       </c>
       <c r="P111" s="7" t="inlineStr">
@@ -8026,7 +8050,11 @@
       </c>
       <c r="I112" s="11" t="inlineStr"/>
       <c r="J112" s="11" t="inlineStr"/>
-      <c r="K112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr">
+        <is>
+          <t>80001529[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="L112" s="11" t="inlineStr"/>
       <c r="M112" s="11" t="inlineStr"/>
       <c r="N112" s="7" t="inlineStr">
@@ -8036,7 +8064,7 @@
       </c>
       <c r="O112" s="11" t="inlineStr">
         <is>
-          <t>오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
+          <t>볼보 부품 카탈로그(EX30 Key Card 80001529, CH-624564), 오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
         </is>
       </c>
       <c r="P112" s="7" t="inlineStr">
@@ -8076,7 +8104,11 @@
       </c>
       <c r="I113" s="11" t="inlineStr"/>
       <c r="J113" s="11" t="inlineStr"/>
-      <c r="K113" s="11" t="inlineStr"/>
+      <c r="K113" s="11" t="inlineStr">
+        <is>
+          <t>80001529[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
       <c r="N113" s="7" t="inlineStr">
@@ -8086,7 +8118,7 @@
       </c>
       <c r="O113" s="11" t="inlineStr">
         <is>
-          <t>오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
+          <t>볼보 부품 카탈로그(EX30 Key Card 80001529, CH-624564), 오토뷰·블로터(EX30 2023.11 사전예약, 2024 국내 출시 — 카드키·디지털키) — 키 칩 자료 없음</t>
         </is>
       </c>
       <c r="P113" s="7" t="inlineStr">
@@ -12328,7 +12360,7 @@
           <t>△</t>
         </is>
       </c>
-      <c r="G175" s="8" t="inlineStr">
+      <c r="G175" s="11" t="inlineStr">
         <is>
           <t>ID48</t>
         </is>
@@ -12351,21 +12383,17 @@
       <c r="K175" s="11" t="inlineStr"/>
       <c r="L175" s="11" t="inlineStr"/>
       <c r="M175" s="11" t="inlineStr"/>
-      <c r="N175" s="8" t="inlineStr">
+      <c r="N175" s="11" t="inlineStr">
         <is>
           <t>CEM</t>
         </is>
       </c>
       <c r="O175" s="11" t="inlineStr">
         <is>
-          <t>transpondery(XC90 2003–2015 Megamos Crypto 48), 2세대 2015 출시 전 재고분</t>
-        </is>
-      </c>
-      <c r="P175" s="8" t="inlineStr">
-        <is>
-          <t>1세대 마지막 연식 — 국내 2015년식 존재 여부 확인 필요</t>
-        </is>
-      </c>
+          <t>transpondery(XC90 2003–2015 Megamos Crypto 48), 다음자동차(XC90 1세대 2015년식 국내 판매), 나무위키(1세대 2015.4 생산 종료, 2세대 2015.5 판매 시작)</t>
+        </is>
+      </c>
+      <c r="P175" s="11" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
